--- a/data/player_stat.xlsx
+++ b/data/player_stat.xlsx
@@ -5,26 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/weeks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="471" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6DFB8B4-F557-42F0-8EA1-42DF3FD2DFCE}"/>
+  <xr:revisionPtr revIDLastSave="484" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8327BFD4-E3F5-41FE-B6E8-DF994323D5AB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Record_Date" sheetId="17" r:id="rId1"/>
-    <sheet name="W01" sheetId="6" r:id="rId2"/>
-    <sheet name="W02" sheetId="7" r:id="rId3"/>
-    <sheet name="W03" sheetId="8" r:id="rId4"/>
-    <sheet name="W04" sheetId="9" r:id="rId5"/>
-    <sheet name="W05" sheetId="10" r:id="rId6"/>
-    <sheet name="W06" sheetId="11" r:id="rId7"/>
-    <sheet name="W07" sheetId="12" r:id="rId8"/>
-    <sheet name="W08" sheetId="13" r:id="rId9"/>
-    <sheet name="W09" sheetId="14" r:id="rId10"/>
-    <sheet name="W010" sheetId="15" r:id="rId11"/>
-    <sheet name="W011" sheetId="16" r:id="rId12"/>
+    <sheet name="W02" sheetId="6" r:id="rId2"/>
+    <sheet name="W03" sheetId="7" r:id="rId3"/>
+    <sheet name="W04" sheetId="8" r:id="rId4"/>
+    <sheet name="W05" sheetId="9" r:id="rId5"/>
+    <sheet name="W06" sheetId="10" r:id="rId6"/>
+    <sheet name="W07" sheetId="11" r:id="rId7"/>
+    <sheet name="W08" sheetId="12" r:id="rId8"/>
+    <sheet name="W09" sheetId="13" r:id="rId9"/>
+    <sheet name="W10" sheetId="14" r:id="rId10"/>
+    <sheet name="W011" sheetId="15" r:id="rId11"/>
+    <sheet name="W012" sheetId="16" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -265,9 +265,6 @@
     <t>Data</t>
   </si>
   <si>
-    <t>W01</t>
-  </si>
-  <si>
     <t>W03</t>
   </si>
   <si>
@@ -296,6 +293,9 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>W12</t>
   </si>
 </sst>
 </file>
@@ -303,7 +303,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="dd\ mmm\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -382,7 +382,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,12 +721,12 @@
         <v>72</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B2" s="5">
         <v>46187</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B3" s="5">
         <v>46194</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B12" s="5">
         <v>46257</v>

--- a/data/player_stat.xlsx
+++ b/data/player_stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="484" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8327BFD4-E3F5-41FE-B6E8-DF994323D5AB}"/>
+  <xr:revisionPtr revIDLastSave="626" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB53DC71-C310-45F6-86AC-8CADF2156BF5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Record_Date" sheetId="17" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="W10" sheetId="14" r:id="rId10"/>
     <sheet name="W011" sheetId="15" r:id="rId11"/>
     <sheet name="W012" sheetId="16" r:id="rId12"/>
+    <sheet name="W013" sheetId="19" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="97">
   <si>
     <t>Name</t>
   </si>
@@ -296,15 +297,51 @@
   </si>
   <si>
     <t>W12</t>
+  </si>
+  <si>
+    <t>23 Aug 2026 - Lose</t>
+  </si>
+  <si>
+    <t>16 Aug 2026 - Win</t>
+  </si>
+  <si>
+    <t>W13</t>
+  </si>
+  <si>
+    <t>30 Aug 2026 - Win</t>
+  </si>
+  <si>
+    <t>09 Aug 2026 - Win</t>
+  </si>
+  <si>
+    <t>26 Jul 2026 - Win</t>
+  </si>
+  <si>
+    <t>05 Jul 2026 - Win</t>
+  </si>
+  <si>
+    <t>21 Jun 2026 - Win</t>
+  </si>
+  <si>
+    <t>14 Jun 2026 - Win</t>
+  </si>
+  <si>
+    <t>02 Aug 2026 - Lose</t>
+  </si>
+  <si>
+    <t>19 Jul 2026 - Lose</t>
+  </si>
+  <si>
+    <t>12 Jul 2026 - Lose</t>
+  </si>
+  <si>
+    <t>28 Jun 2026 - Lose</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
-  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -372,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -382,12 +419,21 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -710,17 +756,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E9160B-48C2-40E4-8623-EBFD7C6323C5}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>72</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>82</v>
       </c>
     </row>
@@ -728,88 +774,96 @@
       <c r="A2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="5">
-        <v>46187</v>
+      <c r="B2" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="5">
-        <v>46194</v>
+      <c r="B3" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="5">
-        <v>46201</v>
+      <c r="B4" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="5">
-        <v>46208</v>
+      <c r="B5" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="5">
-        <v>46215</v>
+      <c r="B6" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="5">
-        <v>46222</v>
+      <c r="B7" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="5">
-        <v>46229</v>
+      <c r="B8" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="5">
-        <v>46236</v>
+      <c r="B9" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="5">
-        <v>46243</v>
+      <c r="B10" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="5">
-        <v>46250</v>
+      <c r="B11" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="5">
-        <v>46257</v>
+      <c r="B12" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2369,7 +2423,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3178,6 +3232,825 @@
       </c>
       <c r="F31">
         <v>5</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A31">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C497D7-4B0F-4C36-9FE9-B821F936F0E5}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="2">
+        <v>7120</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="2">
+        <v>6455</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="2">
+        <v>168</v>
+      </c>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="H29" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>9</v>
       </c>
       <c r="G31">
         <v>4</v>

--- a/data/player_stat.xlsx
+++ b/data/player_stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="626" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB53DC71-C310-45F6-86AC-8CADF2156BF5}"/>
+  <xr:revisionPtr revIDLastSave="636" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC75E9FA-51CF-4E50-A41F-9213731381F5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Record_Date" sheetId="17" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -287,61 +287,37 @@
     <t>W09</t>
   </si>
   <si>
-    <t>W10</t>
-  </si>
-  <si>
-    <t>W11</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>W12</t>
-  </si>
-  <si>
-    <t>23 Aug 2026 - Lose</t>
-  </si>
-  <si>
-    <t>16 Aug 2026 - Win</t>
-  </si>
-  <si>
-    <t>W13</t>
-  </si>
-  <si>
-    <t>30 Aug 2026 - Win</t>
-  </si>
-  <si>
-    <t>09 Aug 2026 - Win</t>
-  </si>
-  <si>
-    <t>26 Jul 2026 - Win</t>
-  </si>
-  <si>
-    <t>05 Jul 2026 - Win</t>
-  </si>
-  <si>
-    <t>21 Jun 2026 - Win</t>
-  </si>
-  <si>
-    <t>14 Jun 2026 - Win</t>
-  </si>
-  <si>
-    <t>02 Aug 2026 - Lose</t>
-  </si>
-  <si>
-    <t>19 Jul 2026 - Lose</t>
-  </si>
-  <si>
-    <t>12 Jul 2026 - Lose</t>
-  </si>
-  <si>
-    <t>28 Jun 2026 - Lose</t>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Win</t>
+  </si>
+  <si>
+    <t>Lose</t>
+  </si>
+  <si>
+    <t>W010</t>
+  </si>
+  <si>
+    <t>W011</t>
+  </si>
+  <si>
+    <t>W012</t>
+  </si>
+  <si>
+    <t>W013</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd\ mmmm\ yyyy"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -409,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -419,6 +395,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -756,114 +733,153 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E9160B-48C2-40E4-8623-EBFD7C6323C5}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.77734375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="C1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="5">
+        <v>46187</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="5">
+        <v>46194</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="5">
+        <v>46201</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="5">
+        <v>46208</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="5">
+        <v>46215</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="5">
+        <v>46222</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="5">
+        <v>46229</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="5">
+        <v>46250</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46257</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="2" t="s">
         <v>87</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46264</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/player_stat.xlsx
+++ b/data/player_stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="636" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC75E9FA-51CF-4E50-A41F-9213731381F5}"/>
+  <xr:revisionPtr revIDLastSave="778" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{115B003F-A83F-4E3C-9B34-6F3F65CE9FEE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Record_Date" sheetId="17" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="W011" sheetId="15" r:id="rId11"/>
     <sheet name="W012" sheetId="16" r:id="rId12"/>
     <sheet name="W013" sheetId="19" r:id="rId13"/>
+    <sheet name="W014" sheetId="20" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="91">
   <si>
     <t>Name</t>
   </si>
@@ -309,6 +310,15 @@
   </si>
   <si>
     <t>W013</t>
+  </si>
+  <si>
+    <t>W014</t>
+  </si>
+  <si>
+    <t>Luminus</t>
+  </si>
+  <si>
+    <t>CloverZ</t>
   </si>
 </sst>
 </file>
@@ -400,7 +410,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -733,10 +753,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E9160B-48C2-40E4-8623-EBFD7C6323C5}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -880,6 +900,17 @@
       </c>
       <c r="C13" s="2" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46271</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2439,7 +2470,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3258,7 +3289,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4077,7 +4108,826 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5138DCC0-1090-412A-B45D-3015CCF5995B}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>6</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15">
+        <v>3481</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="2">
+        <v>6455</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18">
+        <v>2886</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="2">
+        <v>168</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="H29" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A31">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/player_stat.xlsx
+++ b/data/player_stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="778" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{115B003F-A83F-4E3C-9B34-6F3F65CE9FEE}"/>
+  <xr:revisionPtr revIDLastSave="911" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B48D505B-068C-46AF-9BE9-8E43A49F5803}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Record_Date" sheetId="17" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="W012" sheetId="16" r:id="rId12"/>
     <sheet name="W013" sheetId="19" r:id="rId13"/>
     <sheet name="W014" sheetId="20" r:id="rId14"/>
+    <sheet name="W015" sheetId="21" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="94">
   <si>
     <t>Name</t>
   </si>
@@ -320,6 +321,15 @@
   <si>
     <t>CloverZ</t>
   </si>
+  <si>
+    <t>W015</t>
+  </si>
+  <si>
+    <t>หอมหอย</t>
+  </si>
+  <si>
+    <t>GMMFAFA</t>
+  </si>
 </sst>
 </file>
 
@@ -395,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -406,11 +416,27 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -753,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E9160B-48C2-40E4-8623-EBFD7C6323C5}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -911,6 +937,17 @@
       </c>
       <c r="C14" s="2" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46278</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2470,7 +2507,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3289,7 +3326,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4108,7 +4145,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4927,9 +4964,836 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A31">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A671812-3949-42DC-8D9E-0BF15D025A6C}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="6">
+        <v>7351</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="6">
+        <v>3481</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="6">
+        <v>4713</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="7">
+        <v>6455</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="6">
+        <v>2886</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="7">
+        <v>168</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="H29" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:H31">
+    <sortCondition ref="A6:A31"/>
+  </sortState>
+  <conditionalFormatting sqref="A1:A31">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
